--- a/tools/protocol_settlement/附件三 OTA 月度对账底稿付款通知书 模板.xlsx
+++ b/tools/protocol_settlement/附件三 OTA 月度对账底稿付款通知书 模板.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\larfe\Qingyuan\tools\protocol_settlement\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7FB9EE-D01F-4CD8-A97F-AF37456A80F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12200"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="27" r:id="rId1"/>
@@ -72,7 +78,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>Subject</t>
     </r>
@@ -96,7 +102,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -112,7 +118,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -173,7 +179,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -189,7 +195,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -205,7 +211,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -221,7 +227,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -237,7 +243,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -253,7 +259,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -269,7 +275,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -285,7 +291,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -301,7 +307,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -317,7 +323,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -333,7 +339,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -349,7 +355,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -365,7 +371,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -381,7 +387,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -397,7 +403,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -413,7 +419,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -429,7 +435,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -445,7 +451,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -471,7 +477,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -497,7 +503,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">: </t>
     </r>
@@ -513,7 +519,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -531,7 +537,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>: 2018021509200215984</t>
     </r>
@@ -565,7 +571,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -581,7 +587,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -597,7 +603,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -613,7 +619,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -629,7 +635,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -645,7 +651,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -661,7 +667,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -677,7 +683,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -693,7 +699,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -725,15 +731,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -745,7 +748,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -756,7 +759,7 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
@@ -766,7 +769,7 @@
     <font>
       <sz val="16"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -777,7 +780,7 @@
       <b/>
       <sz val="12"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -789,7 +792,7 @@
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -801,7 +804,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -813,12 +816,12 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -828,150 +831,13 @@
     <font>
       <sz val="9"/>
       <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -979,202 +845,22 @@
       <name val="楷体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="18">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1271,254 +957,15 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="52">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1528,7 +975,7 @@
       <alignment vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1572,18 +1019,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1598,14 +1039,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1634,232 +1069,178 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="52">
+  <cellStyles count="5">
+    <cellStyle name="Comma 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="常规 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
     <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="Comma 2" xfId="49"/>
-    <cellStyle name="常规 2" xfId="50"/>
-    <cellStyle name="常规 3" xfId="51"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>952500</xdr:colOff>
+      <xdr:colOff>838200</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>809624</xdr:colOff>
+      <xdr:colOff>908050</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>200143</xdr:rowOff>
+      <xdr:rowOff>154157</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 1"/>
+        <xdr:cNvPr id="4" name="图片 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3185EEDA-0CD4-BB1D-277E-84282F0D253A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1872,8 +1253,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2830195" y="123825"/>
-          <a:ext cx="1864995" cy="962025"/>
+          <a:off x="2711450" y="139700"/>
+          <a:ext cx="2076450" cy="897107"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2166,34 +1547,35 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A3:K98"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.7545454545455" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1272727272727" style="2" customWidth="1"/>
-    <col min="3" max="3" width="28.7545454545455" style="3" customWidth="1"/>
-    <col min="4" max="4" width="27.6272727272727" style="4" customWidth="1"/>
-    <col min="5" max="5" width="17.2545454545455" style="5" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="9.37272727272727" style="5" customWidth="1"/>
-    <col min="7" max="7" width="14.2545454545455" style="3" customWidth="1"/>
-    <col min="8" max="8" width="5.37272727272727" style="5" customWidth="1"/>
-    <col min="9" max="9" width="24.8727272727273" style="5" customWidth="1"/>
-    <col min="10" max="10" width="16.2545454545455" style="5" customWidth="1"/>
-    <col min="11" max="11" width="16.1272727272727" style="5" customWidth="1"/>
+    <col min="1" max="1" width="12.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="28.7265625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="27.6328125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="17.26953125" style="5" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="9.36328125" style="5" customWidth="1"/>
+    <col min="7" max="7" width="14.26953125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="5.36328125" style="5" customWidth="1"/>
+    <col min="9" max="9" width="24.90625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="16.26953125" style="5" customWidth="1"/>
+    <col min="11" max="11" width="16.08984375" style="5" customWidth="1"/>
     <col min="12" max="14" width="9" style="5"/>
-    <col min="15" max="15" width="12.7545454545455" style="5" customWidth="1"/>
+    <col min="15" max="15" width="12.7265625" style="5" customWidth="1"/>
     <col min="16" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="3" ht="14.25" customHeight="1" spans="1:8">
+    <row r="3" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
       <c r="B3" s="7"/>
       <c r="C3" s="8"/>
@@ -2203,7 +1585,7 @@
       <c r="G3" s="11"/>
       <c r="H3" s="10"/>
     </row>
-    <row r="4" ht="13.5" customHeight="1" spans="1:8">
+    <row r="4" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
       <c r="B4" s="7"/>
       <c r="C4" s="8"/>
@@ -2213,7 +1595,7 @@
       <c r="G4" s="11"/>
       <c r="H4" s="10"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="12"/>
       <c r="C5" s="11"/>
@@ -2223,41 +1605,41 @@
       <c r="G5" s="11"/>
       <c r="H5" s="10"/>
     </row>
-    <row r="6" ht="19.5" customHeight="1" spans="1:8">
+    <row r="6" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="12"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
       <c r="F6" s="10"/>
       <c r="G6" s="11"/>
       <c r="H6" s="10"/>
     </row>
-    <row r="7" ht="19.5" customHeight="1" spans="1:8">
+    <row r="7" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
       <c r="B7" s="12"/>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="14"/>
+      <c r="D7" s="66"/>
       <c r="E7" s="14"/>
       <c r="F7" s="10"/>
       <c r="G7" s="11"/>
       <c r="H7" s="10"/>
     </row>
-    <row r="8" ht="14.25" customHeight="1" spans="1:8">
+    <row r="8" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
       <c r="B8" s="12"/>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
       <c r="F8" s="10"/>
       <c r="G8" s="11"/>
       <c r="H8" s="10"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
       <c r="B9" s="12"/>
       <c r="C9" s="11"/>
@@ -2265,341 +1647,340 @@
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
       <c r="G9" s="11"/>
-      <c r="H9" s="17"/>
-    </row>
-    <row r="10" ht="17.25" customHeight="1" spans="1:8">
-      <c r="A10" s="18" t="s">
+      <c r="H9" s="15"/>
+    </row>
+    <row r="10" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="20"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="18"/>
       <c r="D10" s="13"/>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="19" t="s">
         <v>3</v>
       </c>
       <c r="G10" s="11"/>
-      <c r="H10" s="22"/>
-    </row>
-    <row r="11" ht="17.25" customHeight="1" spans="1:8">
-      <c r="A11" s="23" t="s">
+      <c r="H10" s="20"/>
+    </row>
+    <row r="11" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="20"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="18"/>
       <c r="D11" s="13"/>
-      <c r="F11" s="21" t="s">
+      <c r="F11" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="24" t="s">
+      <c r="G11" s="21" t="s">
         <v>6</v>
       </c>
       <c r="H11" s="10"/>
     </row>
-    <row r="12" ht="17.25" customHeight="1" spans="1:8">
+    <row r="12" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="20"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="18"/>
       <c r="D12" s="13"/>
-      <c r="F12" s="21"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="11"/>
       <c r="H12" s="10"/>
     </row>
-    <row r="13" ht="17.25" customHeight="1" spans="1:8">
-      <c r="A13" s="25" t="s">
+    <row r="13" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="20"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="18"/>
       <c r="D13" s="13"/>
-      <c r="E13" s="21"/>
+      <c r="E13" s="19"/>
       <c r="F13" s="10"/>
       <c r="G13" s="11"/>
       <c r="H13" s="10"/>
     </row>
-    <row r="14" ht="17.25" customHeight="1" spans="1:8">
+    <row r="14" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="13"/>
-      <c r="E14" s="21"/>
+      <c r="E14" s="19"/>
       <c r="F14" s="10"/>
       <c r="G14" s="11"/>
       <c r="H14" s="10"/>
     </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="26"/>
-      <c r="B15" s="27" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
+      <c r="B15" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="32" t="s">
+      <c r="C15" s="24"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="H15" s="33"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="34"/>
-      <c r="B16" s="35" t="s">
+      <c r="H15" s="29"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="30"/>
+      <c r="B16" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="35"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="39" t="s">
+      <c r="C16" s="69"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="H16" s="40"/>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" s="41" t="s">
+      <c r="H16" s="33"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="42" t="s">
+      <c r="B17" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="43" t="s">
+      <c r="C17" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="43"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="33"/>
-    </row>
-    <row r="18" ht="18" customHeight="1" spans="1:11">
-      <c r="A18" s="45"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="46" t="s">
+      <c r="D17" s="70"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="29"/>
+    </row>
+    <row r="18" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="36"/>
+      <c r="C18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="47"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="49" t="s">
+      <c r="D18" s="37"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="H18" s="50"/>
-    </row>
-    <row r="19" ht="18.75" customHeight="1" spans="1:11">
-      <c r="A19" s="51"/>
-      <c r="B19" s="52"/>
-      <c r="C19" s="52"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="53"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="50"/>
-      <c r="K19" s="54"/>
-    </row>
-    <row r="20" ht="18.75" customHeight="1" spans="1:11">
-      <c r="A20" s="51"/>
-      <c r="B20" s="52"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="53"/>
-      <c r="G20" s="49"/>
-      <c r="H20" s="50"/>
-      <c r="K20" s="54"/>
-    </row>
-    <row r="21" ht="18.75" customHeight="1" spans="1:11">
-      <c r="A21" s="51"/>
-      <c r="B21" s="52"/>
-      <c r="C21" s="52"/>
-      <c r="D21" s="46"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="49"/>
-      <c r="H21" s="50"/>
-      <c r="K21" s="54"/>
-    </row>
-    <row r="22" ht="18.75" customHeight="1" spans="1:11">
-      <c r="A22" s="51"/>
-      <c r="B22" s="52"/>
-      <c r="C22" s="52"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="53"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="50"/>
-      <c r="K22" s="54"/>
-    </row>
-    <row r="23" ht="18.75" customHeight="1" spans="1:11">
-      <c r="A23" s="51"/>
-      <c r="C23" s="52"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="50"/>
-      <c r="K23" s="54"/>
-    </row>
-    <row r="24" ht="18.75" customHeight="1" spans="1:11">
-      <c r="A24" s="51"/>
-      <c r="B24" s="52"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="53"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="50"/>
-      <c r="K24" s="54"/>
-    </row>
-    <row r="25" ht="18.75" customHeight="1" spans="1:11">
-      <c r="A25" s="51"/>
-      <c r="B25" s="52"/>
-      <c r="C25" s="52"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="53"/>
-      <c r="G25" s="55"/>
-      <c r="H25" s="50"/>
-      <c r="K25" s="54"/>
-    </row>
-    <row r="26" ht="18.75" customHeight="1" spans="1:11">
-      <c r="A26" s="51"/>
-      <c r="B26" s="52"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="55"/>
-      <c r="H26" s="50"/>
-      <c r="K26" s="54"/>
-    </row>
-    <row r="27" ht="18.75" customHeight="1" spans="1:11">
-      <c r="A27" s="51"/>
-      <c r="B27" s="52"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="53"/>
-      <c r="G27" s="55"/>
-      <c r="H27" s="50"/>
-      <c r="K27" s="54"/>
-    </row>
-    <row r="28" ht="18.75" customHeight="1" spans="1:11">
-      <c r="A28" s="51"/>
-      <c r="B28" s="52"/>
-      <c r="C28" s="52"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="53"/>
-      <c r="G28" s="55"/>
-      <c r="H28" s="50"/>
-      <c r="K28" s="54"/>
-    </row>
-    <row r="29" ht="18.75" customHeight="1" spans="1:11">
-      <c r="A29" s="51"/>
-      <c r="B29" s="52"/>
-      <c r="C29" s="52"/>
-      <c r="D29" s="52"/>
-      <c r="E29" s="46"/>
-      <c r="F29" s="53"/>
-      <c r="G29" s="49"/>
-      <c r="H29" s="50"/>
-      <c r="K29" s="54"/>
-    </row>
-    <row r="30" ht="18.75" customHeight="1" spans="1:11">
-      <c r="A30" s="51"/>
-      <c r="B30" s="52"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="53"/>
-      <c r="G30" s="49"/>
-      <c r="H30" s="50"/>
-      <c r="K30" s="54"/>
-    </row>
-    <row r="31" ht="18.75" customHeight="1" spans="1:11">
-      <c r="A31" s="51"/>
-      <c r="B31" s="52"/>
-      <c r="C31" s="52"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="46"/>
-      <c r="F31" s="53"/>
-      <c r="G31" s="49"/>
-      <c r="H31" s="50"/>
-      <c r="K31" s="54"/>
-    </row>
-    <row r="32" ht="18.75" customHeight="1" spans="1:11">
-      <c r="A32" s="51"/>
-      <c r="B32" s="52"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="46"/>
-      <c r="F32" s="53"/>
-      <c r="G32" s="55"/>
-      <c r="H32" s="50"/>
-      <c r="K32" s="54"/>
-    </row>
-    <row r="33" ht="18.75" customHeight="1" spans="1:9">
-      <c r="A33" s="56"/>
-      <c r="B33" s="52"/>
-      <c r="C33" s="57"/>
-      <c r="D33" s="46"/>
-      <c r="E33" s="46"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="58"/>
-      <c r="H33" s="50"/>
-    </row>
-    <row r="34" ht="18" customHeight="1" spans="1:9">
-      <c r="A34" s="59"/>
-      <c r="B34" s="60"/>
-      <c r="C34" s="61" t="s">
+      <c r="H18" s="40"/>
+    </row>
+    <row r="19" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="41"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="40"/>
+      <c r="K19" s="44"/>
+    </row>
+    <row r="20" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="41"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="40"/>
+      <c r="K20" s="44"/>
+    </row>
+    <row r="21" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="41"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="40"/>
+      <c r="K21" s="44"/>
+    </row>
+    <row r="22" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="41"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="40"/>
+      <c r="K22" s="44"/>
+    </row>
+    <row r="23" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="41"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="40"/>
+      <c r="K23" s="44"/>
+    </row>
+    <row r="24" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="41"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="40"/>
+      <c r="K24" s="44"/>
+    </row>
+    <row r="25" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="41"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="40"/>
+      <c r="K25" s="44"/>
+    </row>
+    <row r="26" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="41"/>
+      <c r="B26" s="42"/>
+      <c r="C26" s="42"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="40"/>
+      <c r="K26" s="44"/>
+    </row>
+    <row r="27" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="41"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="40"/>
+      <c r="K27" s="44"/>
+    </row>
+    <row r="28" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="41"/>
+      <c r="B28" s="42"/>
+      <c r="C28" s="42"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="40"/>
+      <c r="K28" s="44"/>
+    </row>
+    <row r="29" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="41"/>
+      <c r="B29" s="42"/>
+      <c r="C29" s="42"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="40"/>
+      <c r="K29" s="44"/>
+    </row>
+    <row r="30" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="41"/>
+      <c r="B30" s="42"/>
+      <c r="C30" s="42"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="40"/>
+      <c r="K30" s="44"/>
+    </row>
+    <row r="31" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="41"/>
+      <c r="B31" s="42"/>
+      <c r="C31" s="42"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="40"/>
+      <c r="K31" s="44"/>
+    </row>
+    <row r="32" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="41"/>
+      <c r="B32" s="42"/>
+      <c r="C32" s="42"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="40"/>
+      <c r="K32" s="44"/>
+    </row>
+    <row r="33" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="45"/>
+      <c r="B33" s="42"/>
+      <c r="C33" s="44"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="40"/>
+    </row>
+    <row r="34" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="34"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="D34" s="60"/>
-      <c r="E34" s="62"/>
-      <c r="F34" s="63"/>
-      <c r="G34" s="64">
+      <c r="D34" s="17"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="50">
         <v>-0.01</v>
       </c>
-      <c r="H34" s="65"/>
-      <c r="I34" s="66"/>
-    </row>
-    <row r="35" ht="21" customHeight="1" spans="1:9">
-      <c r="A35" s="26"/>
-      <c r="B35" s="27"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="33"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="67"/>
-      <c r="H35" s="68"/>
-    </row>
-    <row r="36" ht="21" customHeight="1" spans="1:9">
-      <c r="A36" s="34"/>
-      <c r="B36" s="69"/>
-      <c r="C36" s="35"/>
-      <c r="D36" s="35"/>
-      <c r="E36" s="70"/>
-      <c r="F36" s="63" t="s">
+      <c r="H34" s="51"/>
+      <c r="I34" s="52"/>
+    </row>
+    <row r="35" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="22"/>
+      <c r="B35" s="23"/>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="53"/>
+      <c r="H35" s="54"/>
+    </row>
+    <row r="36" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="30"/>
+      <c r="B36" s="55"/>
+      <c r="C36" s="69"/>
+      <c r="D36" s="69"/>
+      <c r="E36" s="56"/>
+      <c r="F36" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="G36" s="71">
+      <c r="G36" s="57">
         <f>SUM(G18:G34)</f>
         <v>-0.01</v>
       </c>
-      <c r="H36" s="65"/>
-    </row>
-    <row r="37" ht="23.25" customHeight="1" spans="1:9">
+      <c r="H36" s="51"/>
+    </row>
+    <row r="37" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6"/>
       <c r="B37" s="12"/>
       <c r="C37" s="11"/>
       <c r="D37" s="13"/>
       <c r="E37" s="10"/>
-      <c r="H37" s="72"/>
-    </row>
-    <row r="38" spans="1:9">
+      <c r="H37" s="58"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>20</v>
       </c>
@@ -2608,7 +1989,7 @@
       <c r="D38" s="13"/>
       <c r="E38" s="10"/>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>21</v>
       </c>
@@ -2616,11 +1997,11 @@
       <c r="C39" s="11"/>
       <c r="D39" s="13"/>
       <c r="E39" s="10"/>
-      <c r="F39" s="73"/>
-      <c r="G39" s="73"/>
-      <c r="H39" s="73"/>
-    </row>
-    <row r="40" spans="1:9">
+      <c r="F39" s="72"/>
+      <c r="G39" s="72"/>
+      <c r="H39" s="72"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>22</v>
       </c>
@@ -2629,7 +2010,7 @@
       <c r="D40" s="13"/>
       <c r="E40" s="10"/>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
         <v>23</v>
       </c>
@@ -2638,8 +2019,8 @@
       <c r="D41" s="13"/>
       <c r="E41" s="10"/>
     </row>
-    <row r="42" spans="1:9">
-      <c r="A42" s="74" t="s">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="59" t="s">
         <v>24</v>
       </c>
       <c r="B42" s="12"/>
@@ -2647,19 +2028,19 @@
       <c r="D42" s="13"/>
       <c r="E42" s="10"/>
     </row>
-    <row r="43" spans="1:9">
-      <c r="A43" s="75" t="s">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="B43" s="75"/>
-      <c r="C43" s="75"/>
-      <c r="D43" s="75"/>
-      <c r="E43" s="75"/>
-      <c r="F43" s="75"/>
-      <c r="G43" s="75"/>
-      <c r="H43" s="75"/>
-    </row>
-    <row r="44" spans="1:9">
+      <c r="B43" s="73"/>
+      <c r="C43" s="73"/>
+      <c r="D43" s="73"/>
+      <c r="E43" s="73"/>
+      <c r="F43" s="73"/>
+      <c r="G43" s="73"/>
+      <c r="H43" s="73"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>26</v>
       </c>
@@ -2668,19 +2049,19 @@
       <c r="D44" s="13"/>
       <c r="E44" s="10"/>
       <c r="F44" s="10"/>
-      <c r="G44" s="76"/>
-    </row>
-    <row r="45" spans="1:9">
+      <c r="G44" s="60"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B45" s="77"/>
-      <c r="C45" s="78"/>
-      <c r="D45" s="79"/>
-      <c r="E45" s="80"/>
+      <c r="B45" s="61"/>
+      <c r="C45" s="62"/>
+      <c r="D45" s="63"/>
+      <c r="E45" s="64"/>
       <c r="F45" s="10"/>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>28</v>
       </c>
@@ -2689,7 +2070,7 @@
       <c r="D46" s="13"/>
       <c r="F46" s="10"/>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
         <v>29</v>
       </c>
@@ -2697,15 +2078,15 @@
       <c r="C47" s="11"/>
       <c r="D47" s="13"/>
     </row>
-    <row r="48" spans="1:9">
-      <c r="A48" s="81" t="s">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="65" t="s">
         <v>30</v>
       </c>
       <c r="B48" s="12"/>
       <c r="C48" s="11"/>
       <c r="D48" s="13"/>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>31</v>
       </c>
@@ -2713,32 +2094,29 @@
       <c r="C49" s="11"/>
       <c r="D49" s="13"/>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B50" s="82"/>
-      <c r="C50" s="73"/>
-      <c r="D50" s="36"/>
-    </row>
-    <row r="51" spans="1:5">
+      <c r="B50" s="12"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="13"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B51" s="46"/>
-      <c r="C51" s="83"/>
-      <c r="D51" s="84"/>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="25" t="s">
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="16" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="12" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="25" t="s">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="16" t="s">
         <v>36</v>
       </c>
       <c r="B55" s="12"/>
@@ -2746,8 +2124,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="25" t="s">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="16" t="s">
         <v>37</v>
       </c>
       <c r="B56" s="12"/>
@@ -2756,32 +2134,32 @@
         <v>37</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="6"/>
       <c r="B57" s="12"/>
       <c r="E57" s="10"/>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="6"/>
       <c r="B58" s="12"/>
     </row>
-    <row r="98" ht="12" customHeight="1"/>
+    <row r="98" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="A43:H43"/>
     <mergeCell ref="C6:E6"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="A43:H43"/>
   </mergeCells>
+  <phoneticPr fontId="19" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.236220472440945" right="0.236220472440945" top="0.15748031496063" bottom="0" header="0.31496062992126" footer="0.31496062992126"/>
+  <pageMargins left="0.23622047244094499" right="0.23622047244094499" top="0.15748031496063" bottom="0" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="90" fitToHeight="0" orientation="portrait"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/tools/protocol_settlement/附件三 OTA 月度对账底稿付款通知书 模板.xlsx
+++ b/tools/protocol_settlement/附件三 OTA 月度对账底稿付款通知书 模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\larfe\Qingyuan\tools\protocol_settlement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7FB9EE-D01F-4CD8-A97F-AF37456A80F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3942ECA-77DE-4BA1-A961-5E458841E834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -734,7 +734,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -965,7 +965,7 @@
     <xf numFmtId="43" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1166,22 +1166,10 @@
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1189,6 +1177,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1209,61 +1209,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>838200</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>908050</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>154157</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="图片 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3185EEDA-0CD4-BB1D-277E-84282F0D253A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2711450" y="139700"/>
-          <a:ext cx="2076450" cy="897107"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1608,9 +1553,9 @@
     <row r="6" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="12"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
+      <c r="C6" s="70"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="70"/>
       <c r="F6" s="10"/>
       <c r="G6" s="11"/>
       <c r="H6" s="10"/>
@@ -1618,10 +1563,10 @@
     <row r="7" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
       <c r="B7" s="12"/>
-      <c r="C7" s="67" t="s">
+      <c r="C7" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="66"/>
+      <c r="D7" s="70"/>
       <c r="E7" s="14"/>
       <c r="F7" s="10"/>
       <c r="G7" s="11"/>
@@ -1630,11 +1575,11 @@
     <row r="8" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
       <c r="B8" s="12"/>
-      <c r="C8" s="68" t="s">
+      <c r="C8" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
       <c r="F8" s="10"/>
       <c r="G8" s="11"/>
       <c r="H8" s="10"/>
@@ -1728,10 +1673,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="30"/>
-      <c r="B16" s="69" t="s">
+      <c r="B16" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="69"/>
+      <c r="C16" s="67"/>
       <c r="D16" s="13"/>
       <c r="E16" s="10"/>
       <c r="F16" s="31"/>
@@ -1747,10 +1692,10 @@
       <c r="B17" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="70" t="s">
+      <c r="C17" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="70"/>
+      <c r="D17" s="73"/>
       <c r="E17" s="26"/>
       <c r="F17" s="27"/>
       <c r="G17" s="35"/>
@@ -1950,8 +1895,8 @@
     <row r="35" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="22"/>
       <c r="B35" s="23"/>
-      <c r="C35" s="71"/>
-      <c r="D35" s="71"/>
+      <c r="C35" s="66"/>
+      <c r="D35" s="66"/>
       <c r="E35" s="29"/>
       <c r="F35" s="27"/>
       <c r="G35" s="53"/>
@@ -1960,8 +1905,8 @@
     <row r="36" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="30"/>
       <c r="B36" s="55"/>
-      <c r="C36" s="69"/>
-      <c r="D36" s="69"/>
+      <c r="C36" s="67"/>
+      <c r="D36" s="67"/>
       <c r="E36" s="56"/>
       <c r="F36" s="49" t="s">
         <v>19</v>
@@ -1997,9 +1942,9 @@
       <c r="C39" s="11"/>
       <c r="D39" s="13"/>
       <c r="E39" s="10"/>
-      <c r="F39" s="72"/>
-      <c r="G39" s="72"/>
-      <c r="H39" s="72"/>
+      <c r="F39" s="68"/>
+      <c r="G39" s="68"/>
+      <c r="H39" s="68"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
@@ -2029,16 +1974,16 @@
       <c r="E42" s="10"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="73" t="s">
+      <c r="A43" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="B43" s="73"/>
-      <c r="C43" s="73"/>
-      <c r="D43" s="73"/>
-      <c r="E43" s="73"/>
-      <c r="F43" s="73"/>
-      <c r="G43" s="73"/>
-      <c r="H43" s="73"/>
+      <c r="B43" s="69"/>
+      <c r="C43" s="69"/>
+      <c r="D43" s="69"/>
+      <c r="E43" s="69"/>
+      <c r="F43" s="69"/>
+      <c r="G43" s="69"/>
+      <c r="H43" s="69"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
@@ -2160,6 +2105,5 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094499" right="0.23622047244094499" top="0.15748031496063" bottom="0" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="90" fitToHeight="0" orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>